--- a/lecture_slides/11_chapter_multiple_regression/data/autoparts_regression.xlsx
+++ b/lecture_slides/11_chapter_multiple_regression/data/autoparts_regression.xlsx
@@ -396,7 +396,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1651</v>
+        <v>1761</v>
       </c>
       <c r="C2">
         <v>15432</v>
@@ -416,7 +416,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3517</v>
+        <v>3493</v>
       </c>
       <c r="C3">
         <v>51425</v>
@@ -436,7 +436,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3431</v>
+        <v>3450</v>
       </c>
       <c r="C4">
         <v>54496</v>
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1328</v>
+        <v>1445</v>
       </c>
       <c r="C5">
         <v>63234</v>
@@ -476,7 +476,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4677</v>
+        <v>4458</v>
       </c>
       <c r="C6">
         <v>64222</v>
@@ -496,7 +496,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>4699</v>
+        <v>4502</v>
       </c>
       <c r="C7">
         <v>76547</v>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>3704</v>
+        <v>3666</v>
       </c>
       <c r="C8">
         <v>81091</v>
@@ -536,7 +536,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3907</v>
+        <v>3844</v>
       </c>
       <c r="C9">
         <v>81495</v>
@@ -556,7 +556,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2441</v>
+        <v>2549</v>
       </c>
       <c r="C10">
         <v>99660</v>
@@ -576,7 +576,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2550</v>
+        <v>2705</v>
       </c>
       <c r="C11">
         <v>102122</v>
@@ -596,7 +596,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>3887</v>
+        <v>3829</v>
       </c>
       <c r="C12">
         <v>111246</v>
@@ -616,7 +616,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>5112</v>
+        <v>4850</v>
       </c>
       <c r="C13">
         <v>116345</v>
@@ -636,7 +636,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4677</v>
+        <v>4467</v>
       </c>
       <c r="C14">
         <v>118329</v>
@@ -656,7 +656,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2933</v>
+        <v>3089</v>
       </c>
       <c r="C15">
         <v>120915</v>
@@ -676,7 +676,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>4733</v>
+        <v>4523</v>
       </c>
       <c r="C16">
         <v>133281</v>
@@ -696,7 +696,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>4607</v>
+        <v>4401</v>
       </c>
       <c r="C17">
         <v>135325</v>
@@ -716,7 +716,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>3375</v>
+        <v>3586</v>
       </c>
       <c r="C18">
         <v>150982</v>
@@ -736,7 +736,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1764</v>
+        <v>1949</v>
       </c>
       <c r="C19">
         <v>182381</v>
@@ -756,7 +756,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>4360</v>
+        <v>4219</v>
       </c>
       <c r="C20">
         <v>387887</v>
@@ -776,7 +776,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3444</v>
+        <v>3469</v>
       </c>
       <c r="C21">
         <v>389167</v>
@@ -796,7 +796,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2285</v>
+        <v>2511</v>
       </c>
       <c r="C22">
         <v>396904</v>
@@ -816,7 +816,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2734</v>
+        <v>2750</v>
       </c>
       <c r="C23">
         <v>459473</v>
@@ -836,7 +836,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2496</v>
+        <v>2789</v>
       </c>
       <c r="C24">
         <v>527877</v>
@@ -856,7 +856,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2631</v>
+        <v>2916</v>
       </c>
       <c r="C25">
         <v>27486</v>
@@ -876,7 +876,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>2165</v>
+        <v>2267</v>
       </c>
       <c r="C26">
         <v>35436</v>
@@ -896,7 +896,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>2869</v>
+        <v>3139</v>
       </c>
       <c r="C27">
         <v>36788</v>
@@ -916,7 +916,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>1926</v>
+        <v>1939</v>
       </c>
       <c r="C28">
         <v>65415</v>
@@ -936,7 +936,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>3291</v>
+        <v>3668</v>
       </c>
       <c r="C29">
         <v>66395</v>
@@ -956,7 +956,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>2302</v>
+        <v>2645</v>
       </c>
       <c r="C30">
         <v>80210</v>
@@ -976,7 +976,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>1913</v>
+        <v>1878</v>
       </c>
       <c r="C31">
         <v>81438</v>
@@ -996,7 +996,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>1681</v>
+        <v>1556</v>
       </c>
       <c r="C32">
         <v>105833</v>
@@ -1016,7 +1016,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>1272</v>
+        <v>1018</v>
       </c>
       <c r="C33">
         <v>109139</v>
@@ -1036,7 +1036,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>2128</v>
+        <v>2160</v>
       </c>
       <c r="C34">
         <v>110247</v>
@@ -1056,7 +1056,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>2362</v>
+        <v>2441</v>
       </c>
       <c r="C35">
         <v>115501</v>
@@ -1076,7 +1076,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>2069</v>
+        <v>1950</v>
       </c>
       <c r="C36">
         <v>121059</v>
@@ -1096,7 +1096,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>1059</v>
+        <v>848</v>
       </c>
       <c r="C37">
         <v>125624</v>
@@ -1116,7 +1116,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>1691</v>
+        <v>1560</v>
       </c>
       <c r="C38">
         <v>127477</v>
@@ -1136,7 +1136,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>1399</v>
+        <v>1443</v>
       </c>
       <c r="C39">
         <v>156559</v>
@@ -1156,7 +1156,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>1695</v>
+        <v>1555</v>
       </c>
       <c r="C40">
         <v>163039</v>
@@ -1176,7 +1176,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>1502</v>
+        <v>1365</v>
       </c>
       <c r="C41">
         <v>171086</v>
@@ -1196,7 +1196,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="C42">
         <v>192373</v>
@@ -1216,7 +1216,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>2033</v>
+        <v>2343</v>
       </c>
       <c r="C43">
         <v>193961</v>
@@ -1236,7 +1236,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>1460</v>
+        <v>1169</v>
       </c>
       <c r="C44">
         <v>250989</v>
@@ -1256,7 +1256,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>1690</v>
+        <v>1476</v>
       </c>
       <c r="C45">
         <v>380860</v>
@@ -1276,7 +1276,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>2186</v>
+        <v>2232</v>
       </c>
       <c r="C46">
         <v>386399</v>
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>-52.12055</v>
+        <v>40.20434</v>
       </c>
       <c r="C2">
-        <v>250.18343</v>
+        <v>195.95849</v>
       </c>
       <c r="D2">
-        <v>-0.208</v>
+        <v>0.205</v>
       </c>
       <c r="E2">
-        <v>0.836</v>
+        <v>0.8385</v>
       </c>
       <c r="F2">
-        <v>-557.76</v>
+        <v>-355.843</v>
       </c>
       <c r="G2">
-        <v>453.519</v>
+        <v>436.251</v>
       </c>
     </row>
     <row r="3">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.00035</v>
+        <v>0.00032</v>
       </c>
       <c r="C3">
-        <v>0.0004</v>
+        <v>0.00032</v>
       </c>
       <c r="D3">
-        <v>0.876</v>
+        <v>0.999</v>
       </c>
       <c r="E3">
-        <v>0.3863</v>
+        <v>0.3236</v>
       </c>
       <c r="F3">
         <v>-0</v>
@@ -1395,22 +1395,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.00467</v>
+        <v>0.00363</v>
       </c>
       <c r="C4">
-        <v>0.0031</v>
+        <v>0.00243</v>
       </c>
       <c r="D4">
-        <v>1.504</v>
+        <v>1.492</v>
       </c>
       <c r="E4">
-        <v>0.1405</v>
+        <v>0.1436</v>
       </c>
       <c r="F4">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="G4">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1420,22 +1420,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>642.27781</v>
+        <v>639.94354</v>
       </c>
       <c r="C5">
-        <v>38.93831</v>
+        <v>30.49879</v>
       </c>
       <c r="D5">
-        <v>16.495</v>
+        <v>20.983</v>
       </c>
       <c r="E5">
-        <v>1.916E-19</v>
+        <v>3.37E-23</v>
       </c>
       <c r="F5">
-        <v>563.581</v>
+        <v>578.303</v>
       </c>
       <c r="G5">
-        <v>720.975</v>
+        <v>701.5839999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1445,22 +1445,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>816.50944</v>
+        <v>791.08547</v>
       </c>
       <c r="C6">
-        <v>117.06155</v>
+        <v>91.68953999999999</v>
       </c>
       <c r="D6">
-        <v>6.975</v>
+        <v>8.628</v>
       </c>
       <c r="E6">
-        <v>2.032E-08</v>
+        <v>1.137E-10</v>
       </c>
       <c r="F6">
-        <v>579.919</v>
+        <v>605.774</v>
       </c>
       <c r="G6">
-        <v>1053.1</v>
+        <v>976.397</v>
       </c>
     </row>
   </sheetData>
@@ -1470,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9653131057247084</v>
+        <v>0.9779332441776524</v>
       </c>
     </row>
     <row r="3">
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9318293920838822</v>
+        <v>0.9563534300678278</v>
       </c>
     </row>
     <row r="4">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9250123312922703</v>
+        <v>0.9519887730746106</v>
       </c>
     </row>
     <row r="5">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>308.4902364580705</v>
+        <v>241.6278295884287</v>
       </c>
     </row>
     <row r="6">
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>136.690785159269</v>
+        <v>219.1130784283903</v>
       </c>
     </row>
     <row r="8">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>9.225913150930834E-23</v>
+        <v>1.267018375688985E-26</v>
       </c>
     </row>
     <row r="11">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>55840033.64444445</v>
+        <v>53506159.24444444</v>
       </c>
     </row>
     <row r="12">
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>52033384.60484618</v>
+        <v>51170798.92317986</v>
       </c>
     </row>
     <row r="13">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>3806649.039598247</v>
+        <v>2335360.321264588</v>
       </c>
     </row>
     <row r="14">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>13008346.15121154</v>
+        <v>12792699.73079496</v>
       </c>
     </row>
     <row r="15">
@@ -1622,27 +1622,67 @@
         </is>
       </c>
       <c r="B15">
-        <v>95166.22598995618</v>
+        <v>58384.00803161471</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Partial F {yelp,endcap}</t>
+          <t>SSE reduced (yelp + endcap)</t>
         </is>
       </c>
       <c r="B16">
-        <v>266.4944493653217</v>
+        <v>2485954.961100377</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Partial F drop {population, income}</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>1.289690832412893</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Partial F p-value</t>
         </is>
       </c>
-      <c r="B17">
-        <v>7.555716752146314E-24</v>
+      <c r="B18">
+        <v>0.2865581861694097</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Partial F 5% critical (2, 40)</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>3.231726992830843</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Partial F drop income only (= t^2)</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>2.225741514129411</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Partial F income-only p-value</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.1435729167365687</v>
       </c>
     </row>
   </sheetData>
@@ -1746,13 +1786,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.02347496110862981</v>
+        <v>0.02747927397396783</v>
       </c>
       <c r="C2">
-        <v>-0.02302623121953085</v>
+        <v>-0.01883123678917653</v>
       </c>
       <c r="D2">
-        <v>1139.435856929047</v>
+        <v>1113.080761576706</v>
       </c>
     </row>
     <row r="3">
@@ -1762,13 +1802,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.8489147887263736</v>
+        <v>0.8751270099592817</v>
       </c>
       <c r="C3">
-        <v>0.8378597732673277</v>
+        <v>0.8659899619075219</v>
       </c>
       <c r="D3">
-        <v>453.6196773998282</v>
+        <v>403.6864906011448</v>
       </c>
     </row>
     <row r="4">
@@ -1778,13 +1818,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9318293920838822</v>
+        <v>0.9563534300678278</v>
       </c>
       <c r="C4">
-        <v>0.9250123312922703</v>
+        <v>0.9519887730746106</v>
       </c>
       <c r="D4">
-        <v>308.4902364580705</v>
+        <v>241.6278295884287</v>
       </c>
     </row>
   </sheetData>
@@ -1846,7 +1886,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>2815.9</v>
+        <v>2837.2</v>
       </c>
     </row>
     <row r="6">
@@ -1856,7 +1896,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>3632.4</v>
+        <v>3628.3</v>
       </c>
     </row>
     <row r="7">
@@ -1866,7 +1906,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>816.5</v>
+        <v>791.1</v>
       </c>
     </row>
   </sheetData>
